--- a/abtesting_instructions/instructions.xlsx
+++ b/abtesting_instructions/instructions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrii.Rudavskyi\Desktop\ab-testing\abtesting_instructions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucas.zipp/Git_Repos/refining-mediapipe/abtesting_instructions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5856A139-F1A6-4161-A64C-4D52A1CF8318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DC2850-FB1F-AA4F-AB6B-6A84CCFD00A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="63210" yWindow="8865" windowWidth="29955" windowHeight="16320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5040" yWindow="5420" windowWidth="35840" windowHeight="20000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,28 +33,28 @@
     <t>Instruction</t>
   </si>
   <si>
-    <t>Test 1</t>
-  </si>
-  <si>
-    <t>Test 2</t>
-  </si>
-  <si>
-    <t>In normal office lighting conditions position your head roughly 60 cm from the screen. Look at the screen while not moving your head.</t>
-  </si>
-  <si>
-    <t>In normal office lighting conditions position your head roughly 60 cm from the screen. Look at the screen while actively moving your head: first slowly to the left/right, then faster to the left/right, yaw, pitch.</t>
-  </si>
-  <si>
-    <t>Test 3</t>
-  </si>
-  <si>
-    <t>In low lighting environment position your head roughly 60 cm from the screeen.  Look at the screen while not moving your head.</t>
-  </si>
-  <si>
-    <t>Test 4</t>
-  </si>
-  <si>
-    <t>In low lighting conditions position your head roughly 60 cm from the screen. Look at the screen while actively moving your head: first slowly to the left/right, then faster to the left/right, yaw, pitch.</t>
+    <t>Normal office lighting --- Stationary viewing</t>
+  </si>
+  <si>
+    <t>Normal office lighting --- Active movement: Slow+fast left/right, yaw, pitch, roll, etc.</t>
+  </si>
+  <si>
+    <t>Low lighting  --- Stationary viewing</t>
+  </si>
+  <si>
+    <t>Low lighting --- Active movement: Slow+fast left/right, yaw, pitch, roll, etc.</t>
+  </si>
+  <si>
+    <t>Test Condition 1</t>
+  </si>
+  <si>
+    <t>Test Condition 2</t>
+  </si>
+  <si>
+    <t>Test Condition 3</t>
+  </si>
+  <si>
+    <t>Test Condition 4</t>
   </si>
 </sst>
 </file>
@@ -379,13 +379,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -393,36 +393,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
